--- a/one down/普物實驗/14 麥克森干涉實驗/E24146107_王翊權_預報14_表格.xlsx
+++ b/one down/普物實驗/14 麥克森干涉實驗/E24146107_王翊權_預報14_表格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eric Wang\.gemini\Workspaces\school\one down\普物實驗\14 麥克森干涉實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DD6476-9E03-400A-BD9D-5107A9F332B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62826A00-EBC2-4767-8A93-9C15243B5F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="ZcQTRRckLt5QySOlyqzCIFB6ndIJ08qhIfb1CTpMkoE="/>
     </ext>
   </extLst>
 </workbook>
@@ -73,6 +70,9 @@
     <t>測微器平均讀數 (mm)</t>
   </si>
   <si>
+    <t>測微器讀數的平均變化 Δx (mm)</t>
+  </si>
+  <si>
     <t>反射鏡移動距離 Δd (mm)</t>
   </si>
   <si>
@@ -107,76 +107,14 @@
     <t>N</t>
   </si>
   <si>
+    <t>ΔP
+(kPa)</t>
+  </si>
+  <si>
     <t>平均值</t>
   </si>
   <si>
-    <t>測微器讀數的平均變化 Δx (mm)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="4"/>
-        <charset val="161"/>
-      </rPr>
-      <t>Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>n (1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="4"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>-5)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="4"/>
-        <charset val="161"/>
-      </rPr>
-      <t>Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>P
-(kPa)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Δn (1e-5)</t>
   </si>
 </sst>
 </file>
@@ -187,10 +125,10 @@
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="0.000_ "/>
     <numFmt numFmtId="178" formatCode="0.00000_ "/>
-    <numFmt numFmtId="179" formatCode="0.000000"/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
+    <numFmt numFmtId="179" formatCode="0.0"/>
+    <numFmt numFmtId="180" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -227,31 +165,12 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F1F1F"/>
       <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="4"/>
-      <charset val="161"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="4"/>
     </font>
     <font>
       <sz val="12"/>
@@ -287,7 +206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -324,19 +243,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -354,19 +260,6 @@
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -423,19 +316,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -454,19 +334,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -478,19 +345,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -721,19 +575,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -746,18 +587,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -772,22 +721,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -799,97 +733,52 @@
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -898,63 +787,95 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1064,6 +985,7 @@
           <c:spPr>
             <a:ln>
               <a:noFill/>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:marker>
@@ -1077,9 +999,23 @@
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
+                <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>工作表1!$F$16:$J$16</c:f>
@@ -1131,7 +1067,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2D2D-4C66-95A6-7AED2B20F30B}"/>
+              <c16:uniqueId val="{00000000-A337-48C1-A98E-14D3D1F6EB47}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1159,6 +1095,7 @@
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -1213,7 +1150,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln/>
+          <a:ln>
+            <a:prstDash val="solid"/>
+          </a:ln>
         </c:spPr>
         <c:txPr>
           <a:bodyPr/>
@@ -1247,6 +1186,7 @@
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -1292,7 +1232,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln/>
+          <a:ln>
+            <a:prstDash val="solid"/>
+          </a:ln>
         </c:spPr>
         <c:txPr>
           <a:bodyPr/>
@@ -1418,6 +1360,7 @@
           <c:spPr>
             <a:ln>
               <a:noFill/>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:marker>
@@ -1431,9 +1374,18 @@
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
+                <a:prstDash val="solid"/>
               </a:ln>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>工作表1!$F$15:$J$15</c:f>
@@ -1441,19 +1393,19 @@
                 <c:formatCode>0.000_ </c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-0.71249999999999858</c:v>
+                  <c:v>-0.80100000000000193</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-1.3175000000000008</c:v>
+                  <c:v>-1.3989999999999991</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.9344999999999999</c:v>
+                  <c:v>-2.0080000000000009</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-2.5474999999999994</c:v>
+                  <c:v>-2.6270000000000007</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.1934999999999993</c:v>
+                  <c:v>-3.2450000000000028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1485,7 +1437,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-203C-4592-A3C8-FF2827657E8C}"/>
+              <c16:uniqueId val="{00000000-B275-45F1-9CBE-59DEDB0DA2A7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1513,6 +1465,7 @@
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -1567,7 +1520,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln/>
+          <a:ln>
+            <a:prstDash val="solid"/>
+          </a:ln>
         </c:spPr>
         <c:txPr>
           <a:bodyPr/>
@@ -1601,6 +1556,7 @@
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -1646,7 +1602,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
         <c:spPr>
-          <a:ln/>
+          <a:ln>
+            <a:prstDash val="solid"/>
+          </a:ln>
         </c:spPr>
         <c:txPr>
           <a:bodyPr/>
@@ -1684,7 +1642,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
-  <c:roundedCorners val="1"/>
+  <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
@@ -1702,22 +1660,20 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="el-GR" sz="1400" b="0" i="0">
+              <a:rPr lang="el-GR" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
               </a:rPr>
               <a:t>Δ</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0">
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>P</a:t>
+              <a:t>n</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="0" i="0">
@@ -1729,22 +1685,20 @@
               <a:t>對</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="el-GR" sz="1400" b="0" i="0">
+              <a:rPr lang="el-GR" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
               </a:rPr>
               <a:t>Δ</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0">
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>n</a:t>
+              <a:t>P</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="0" i="0">
@@ -1770,16 +1724,61 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln cap="rnd">
+            <a:ln w="19050">
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:marker>
-            <c:spPr>
-              <a:ln cap="rnd"/>
-            </c:spPr>
-          </c:marker>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
+            <c:numRef>
+              <c:f>工作表1!$D$39:$I$39</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>68.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>工作表1!$D$40:$I$40</c:f>
               <c:numCache>
@@ -1805,43 +1804,15 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>工作表1!$D$39:$I$39</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>11.6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.8</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>31.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>41.3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>55.2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>67.3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-6603-4A18-8D70-C3F51B616D89}"/>
+              <c16:uniqueId val="{00000000-58EB-4430-815F-7C182DD508CB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1865,6 +1836,7 @@
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -1874,43 +1846,64 @@
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr sz="1000" b="0" i="0">
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                  <a:lnSpc>
+                    <a:spcPct val="100000"/>
+                  </a:lnSpc>
+                  <a:spcBef>
+                    <a:spcPts val="0"/>
+                  </a:spcBef>
+                  <a:spcAft>
+                    <a:spcPts val="0"/>
+                  </a:spcAft>
+                  <a:buClrTx/>
+                  <a:buSzTx/>
+                  <a:buFontTx/>
+                  <a:buNone/>
+                  <a:tabLst/>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="el-GR" sz="1000" b="0" i="0">
+                  <a:rPr lang="el-GR" altLang="zh-TW" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
                   </a:rPr>
                   <a:t>Δ</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0">
+                  <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
                   </a:rPr>
-                  <a:t>n (1e-5)</a:t>
+                  <a:t>P(kPa)</a:t>
                 </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln/>
+          <a:ln>
+            <a:prstDash val="solid"/>
+          </a:ln>
         </c:spPr>
         <c:txPr>
           <a:bodyPr/>
@@ -1949,12 +1942,20 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="el-GR" altLang="zh-TW"/>
+                  <a:rPr lang="el-GR" altLang="zh-TW" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
                   <a:t>Δ</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="zh-TW"/>
-                  <a:t>P(kPa)</a:t>
+                  <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>n (1e-5)</a:t>
                 </a:r>
                 <a:endParaRPr lang="zh-TW" altLang="en-US"/>
               </a:p>
@@ -1962,13 +1963,14 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="cross"/>
         <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
+            <a:prstDash val="solid"/>
           </a:ln>
         </c:spPr>
         <c:crossAx val="1039393503"/>
@@ -1980,6 +1982,15 @@
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:ln w="15875" cap="rnd">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:tint val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1993,17 +2004,17 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>215265</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>131445</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4438650" cy="3133725"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="269599913" name="Chart 1" title="ΔN對Δd的關係">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A9C41110}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2023,18 +2034,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>554355</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>36195</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4438650" cy="3133725"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="427419038" name="Chart 2">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009EE57919}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2054,18 +2065,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>125186</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>132806</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4895850" cy="3076575"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="676516014" name="Chart 3">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AED05228}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2295,7 +2306,8 @@
     <col min="9" max="9" width="8.796875" style="4" customWidth="1"/>
     <col min="10" max="10" width="9.796875" style="4" customWidth="1"/>
     <col min="11" max="26" width="8.09765625" style="4" customWidth="1"/>
-    <col min="27" max="16384" width="11.19921875" style="4"/>
+    <col min="27" max="29" width="11.19921875" style="4" customWidth="1"/>
+    <col min="30" max="16384" width="11.19921875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2334,21 +2346,11 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="I2" s="3">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3">
-        <v>2.5</v>
-      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -2368,27 +2370,27 @@
     </row>
     <row r="3" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9">
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="6">
         <v>0</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="6">
         <v>10</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="6">
         <v>20</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="6">
         <v>30</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="6">
         <v>40</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="7">
         <v>50</v>
       </c>
       <c r="K3" s="3"/>
@@ -2410,31 +2412,31 @@
     </row>
     <row r="4" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="9">
         <v>10</v>
       </c>
-      <c r="F4" s="15">
-        <v>9.15</v>
+      <c r="F4" s="10">
+        <v>9.16</v>
       </c>
-      <c r="G4" s="15">
-        <v>8.5500000000000007</v>
+      <c r="G4" s="10">
+        <v>8.5399999999999991</v>
       </c>
-      <c r="H4" s="15">
-        <v>7.95</v>
+      <c r="H4" s="10">
+        <v>7.94</v>
       </c>
-      <c r="I4" s="15">
-        <v>7.37</v>
+      <c r="I4" s="10">
+        <v>7.28</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="11">
         <v>6.77</v>
       </c>
       <c r="K4" s="3"/>
@@ -2456,28 +2458,27 @@
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="13" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="15">
-        <v>10.01</v>
+      <c r="E5" s="10">
+        <v>10.029999999999999</v>
       </c>
-      <c r="F5" s="15">
-        <v>9.39</v>
+      <c r="F5" s="10">
+        <v>9.2899999999999991</v>
       </c>
-      <c r="G5" s="15">
-        <v>8.7799999999999994</v>
+      <c r="G5" s="10">
+        <v>8.6999999999999993</v>
       </c>
-      <c r="H5" s="15">
-        <v>8.15</v>
+      <c r="H5" s="10">
+        <v>8.1199999999999992</v>
       </c>
-      <c r="I5" s="15">
-        <v>7.48</v>
+      <c r="I5" s="10">
+        <v>7.47</v>
       </c>
-      <c r="J5" s="19">
-        <f>J4</f>
+      <c r="J5" s="12">
         <v>6.77</v>
       </c>
       <c r="K5" s="3"/>
@@ -2499,30 +2500,30 @@
     </row>
     <row r="6" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="9">
         <v>10</v>
       </c>
-      <c r="F6" s="15">
-        <v>9.31</v>
+      <c r="F6" s="10">
+        <v>9.07</v>
       </c>
-      <c r="G6" s="15">
-        <v>8.6999999999999993</v>
+      <c r="G6" s="10">
+        <v>8.5500000000000007</v>
       </c>
-      <c r="H6" s="15">
-        <v>8.09</v>
+      <c r="H6" s="10">
+        <v>7.87</v>
       </c>
-      <c r="I6" s="15">
-        <v>7.47</v>
+      <c r="I6" s="10">
+        <v>7.31</v>
       </c>
-      <c r="J6" s="16">
-        <v>6.87</v>
+      <c r="J6" s="11">
+        <v>6.77</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -2543,29 +2544,28 @@
     </row>
     <row r="7" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="13" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="15">
-        <v>10.039999999999999</v>
+      <c r="E7" s="10">
+        <v>10.029999999999999</v>
       </c>
-      <c r="F7" s="15">
-        <v>9.42</v>
+      <c r="F7" s="10">
+        <v>9.34</v>
       </c>
-      <c r="G7" s="15">
-        <v>8.82</v>
+      <c r="G7" s="10">
+        <v>8.75</v>
       </c>
-      <c r="H7" s="15">
-        <v>8.17</v>
+      <c r="H7" s="10">
+        <v>8.1</v>
       </c>
-      <c r="I7" s="15">
-        <v>7.54</v>
+      <c r="I7" s="10">
+        <v>7.47</v>
       </c>
-      <c r="J7" s="19">
-        <f>J6</f>
-        <v>6.87</v>
+      <c r="J7" s="12">
+        <v>6.77</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2586,30 +2586,30 @@
     </row>
     <row r="8" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="9">
         <v>10</v>
       </c>
-      <c r="F8" s="15">
-        <v>9.2200000000000006</v>
+      <c r="F8" s="10">
+        <v>9.1</v>
       </c>
-      <c r="G8" s="15">
-        <v>8.6199999999999992</v>
+      <c r="G8" s="10">
+        <v>8.4700000000000006</v>
       </c>
-      <c r="H8" s="15">
-        <v>8.02</v>
+      <c r="H8" s="10">
+        <v>7.9</v>
       </c>
-      <c r="I8" s="15">
-        <v>7.42</v>
+      <c r="I8" s="10">
+        <v>7.32</v>
       </c>
-      <c r="J8" s="16">
-        <v>6.82</v>
+      <c r="J8" s="11">
+        <v>6.77</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -2620,38 +2620,38 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
     </row>
     <row r="9" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="13" t="s">
+      <c r="B9" s="54"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="15">
-        <v>10.02</v>
+      <c r="E9" s="10">
+        <v>10.029999999999999</v>
       </c>
-      <c r="F9" s="15">
-        <v>9.35</v>
+      <c r="F9" s="10">
+        <v>9.34</v>
       </c>
-      <c r="G9" s="15">
-        <v>8.74</v>
+      <c r="G9" s="10">
+        <v>8.7100000000000009</v>
       </c>
-      <c r="H9" s="15">
-        <v>8.1199999999999992</v>
+      <c r="H9" s="10">
+        <v>8.09</v>
       </c>
-      <c r="I9" s="15">
-        <v>7.51</v>
+      <c r="I9" s="10">
+        <v>7.49</v>
       </c>
-      <c r="J9" s="19">
-        <v>6.82</v>
+      <c r="J9" s="12">
+        <v>6.77</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -2662,40 +2662,40 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
     </row>
     <row r="10" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="9">
         <v>10</v>
       </c>
-      <c r="F10" s="15">
-        <v>9.26</v>
+      <c r="F10" s="10">
+        <v>9.08</v>
       </c>
-      <c r="G10" s="15">
-        <v>8.66</v>
+      <c r="G10" s="10">
+        <v>8.49</v>
       </c>
-      <c r="H10" s="15">
-        <v>8.0500000000000007</v>
+      <c r="H10" s="10">
+        <v>7.92</v>
       </c>
-      <c r="I10" s="15">
-        <v>7.45</v>
+      <c r="I10" s="10">
+        <v>7.27</v>
       </c>
-      <c r="J10" s="16">
-        <v>6.84</v>
+      <c r="J10" s="11">
+        <v>6.77</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -2706,38 +2706,38 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="21"/>
-      <c r="W10" s="21"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="21"/>
-      <c r="Z10" s="21"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
     </row>
     <row r="11" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="13" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="10">
         <v>10.029999999999999</v>
       </c>
-      <c r="F11" s="15">
-        <v>9.3800000000000008</v>
+      <c r="F11" s="10">
+        <v>9.2899999999999991</v>
       </c>
-      <c r="G11" s="15">
-        <v>8.77</v>
+      <c r="G11" s="10">
+        <v>8.74</v>
       </c>
-      <c r="H11" s="15">
-        <v>8.14</v>
+      <c r="H11" s="10">
+        <v>8.08</v>
       </c>
-      <c r="I11" s="15">
-        <v>7.52</v>
+      <c r="I11" s="10">
+        <v>7.48</v>
       </c>
-      <c r="J11" s="19">
-        <v>6.84</v>
+      <c r="J11" s="12">
+        <v>6.77</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -2748,40 +2748,40 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
     </row>
     <row r="12" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="54"/>
+      <c r="C12" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="9">
         <v>10</v>
       </c>
-      <c r="F12" s="15">
-        <v>9.19</v>
+      <c r="F12" s="10">
+        <v>9.14</v>
       </c>
-      <c r="G12" s="15">
-        <v>8.59</v>
+      <c r="G12" s="10">
+        <v>8.48</v>
       </c>
-      <c r="H12" s="15">
-        <v>7.98</v>
+      <c r="H12" s="10">
+        <v>7.91</v>
       </c>
-      <c r="I12" s="15">
-        <v>7.39</v>
+      <c r="I12" s="10">
+        <v>7.32</v>
       </c>
-      <c r="J12" s="16">
-        <v>6.79</v>
+      <c r="J12" s="11">
+        <v>6.77</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2792,38 +2792,38 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="21"/>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
     </row>
     <row r="13" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24" t="s">
+      <c r="B13" s="65"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="25">
-        <v>10.015000000000001</v>
+      <c r="E13" s="16">
+        <v>10.029999999999999</v>
       </c>
-      <c r="F13" s="25">
-        <v>9.32</v>
+      <c r="F13" s="16">
+        <v>9.33</v>
       </c>
-      <c r="G13" s="25">
-        <v>8.7100000000000009</v>
+      <c r="G13" s="16">
+        <v>8.73</v>
       </c>
-      <c r="H13" s="25">
-        <v>8.1</v>
+      <c r="H13" s="16">
+        <v>8.14</v>
       </c>
-      <c r="I13" s="25">
-        <v>7.49</v>
+      <c r="I13" s="16">
+        <v>7.47</v>
       </c>
-      <c r="J13" s="26">
-        <v>6.79</v>
+      <c r="J13" s="17">
+        <v>6.77</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2834,44 +2834,44 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
     </row>
     <row r="14" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="27">
+      <c r="C14" s="45"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="18">
         <f t="shared" ref="E14:J14" si="0">AVERAGE(E4:E13)</f>
-        <v>10.0115</v>
+        <v>10.015000000000001</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="18">
         <f t="shared" si="0"/>
-        <v>9.2990000000000013</v>
+        <v>9.2139999999999986</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="18">
         <f t="shared" si="0"/>
-        <v>8.6939999999999991</v>
+        <v>8.6160000000000014</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="18">
         <f t="shared" si="0"/>
-        <v>8.077</v>
+        <v>8.0069999999999997</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="18">
         <f t="shared" si="0"/>
-        <v>7.4640000000000004</v>
+        <v>7.3879999999999999</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="19">
         <f t="shared" si="0"/>
-        <v>6.8180000000000005</v>
+        <v>6.7699999999999978</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -2882,41 +2882,41 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="29" t="s">
-        <v>23</v>
+      <c r="B15" s="59" t="s">
+        <v>11</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="32">
-        <f t="shared" ref="F15:J15" si="1">F14 - $E14</f>
-        <v>-0.71249999999999858</v>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="20">
+        <f>F14 - $E14</f>
+        <v>-0.80100000000000193</v>
       </c>
-      <c r="G15" s="32">
-        <f t="shared" si="1"/>
-        <v>-1.3175000000000008</v>
+      <c r="G15" s="20">
+        <f>G14 - $E14</f>
+        <v>-1.3989999999999991</v>
       </c>
-      <c r="H15" s="32">
-        <f t="shared" si="1"/>
-        <v>-1.9344999999999999</v>
+      <c r="H15" s="20">
+        <f>H14 - $E14</f>
+        <v>-2.0080000000000009</v>
       </c>
-      <c r="I15" s="32">
-        <f t="shared" si="1"/>
-        <v>-2.5474999999999994</v>
+      <c r="I15" s="20">
+        <f>I14 - $E14</f>
+        <v>-2.6270000000000007</v>
       </c>
-      <c r="J15" s="33">
-        <f t="shared" si="1"/>
-        <v>-3.1934999999999993</v>
+      <c r="J15" s="21">
+        <f>J14 - $E14</f>
+        <v>-3.2450000000000028</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -2927,40 +2927,40 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
     </row>
     <row r="16" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
-      <c r="B16" s="29" t="s">
-        <v>11</v>
+      <c r="B16" s="59" t="s">
+        <v>12</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="34">
-        <f t="shared" ref="F16:J16" si="2">633 * 10^-9 * F3 / 2 *1000</f>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="22">
+        <f>633 * 10^-9 * F3 / 2 *1000</f>
         <v>3.1650000000000003E-3</v>
       </c>
-      <c r="G16" s="34">
-        <f t="shared" si="2"/>
+      <c r="G16" s="22">
+        <f>633 * 10^-9 * G3 / 2 *1000</f>
         <v>6.3300000000000006E-3</v>
       </c>
-      <c r="H16" s="34">
-        <f t="shared" si="2"/>
+      <c r="H16" s="22">
+        <f>633 * 10^-9 * H3 / 2 *1000</f>
         <v>9.495E-3</v>
       </c>
-      <c r="I16" s="34">
-        <f t="shared" si="2"/>
+      <c r="I16" s="22">
+        <f>633 * 10^-9 * I3 / 2 *1000</f>
         <v>1.2660000000000001E-2</v>
       </c>
-      <c r="J16" s="35">
-        <f t="shared" si="2"/>
+      <c r="J16" s="23">
+        <f>633 * 10^-9 * J3 / 2 *1000</f>
         <v>1.5825000000000002E-2</v>
       </c>
       <c r="K16" s="3"/>
@@ -2972,30 +2972,30 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="21"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
     </row>
     <row r="17" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
-      <c r="B17" s="36" t="s">
-        <v>12</v>
+      <c r="B17" s="42" t="s">
+        <v>13</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39">
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="49">
         <f>(F16/F15 + G16/G15 + H16/H15 + I16/I15 + J16/J15)/500</f>
-        <v>-4.8159720993724797E-5</v>
+        <v>-4.5800951618360821E-5</v>
       </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="40"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="50"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -3005,13 +3005,13 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
     </row>
     <row r="18" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
@@ -3033,13 +3033,13 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
     </row>
     <row r="19" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
@@ -3064,7 +3064,7 @@
     <row r="20" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -3083,25 +3083,25 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
     </row>
     <row r="21" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
-      <c r="B21" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="43" t="s">
+      <c r="B21" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="C21" s="67"/>
+      <c r="D21" s="24" t="s">
         <v>16</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>17</v>
       </c>
       <c r="F21" s="3"/>
       <c r="I21" s="3"/>
@@ -3115,70 +3115,70 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="45" t="s">
-        <v>17</v>
+      <c r="B22" s="56" t="s">
+        <v>18</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="26" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E22" s="2">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="47"/>
+      <c r="G22" s="27"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
     </row>
     <row r="23" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="46" t="s">
+      <c r="B23" s="57"/>
+      <c r="C23" s="26" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="1">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E23" s="2">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -3194,24 +3194,24 @@
     </row>
     <row r="24" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="46" t="s">
+      <c r="B24" s="57"/>
+      <c r="C24" s="26" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -3227,24 +3227,24 @@
     </row>
     <row r="25" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="46" t="s">
+      <c r="B25" s="57"/>
+      <c r="C25" s="26" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
@@ -3260,24 +3260,24 @@
     </row>
     <row r="26" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="46" t="s">
+      <c r="B26" s="58"/>
+      <c r="C26" s="26" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="1">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
@@ -3293,26 +3293,26 @@
     </row>
     <row r="27" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
-      <c r="B27" s="50" t="s">
-        <v>18</v>
+      <c r="B27" s="62" t="s">
+        <v>19</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="46">
-        <f t="shared" ref="D27:E27" si="3">AVERAGE(D22:D26)</f>
-        <v>98</v>
+      <c r="C27" s="63"/>
+      <c r="D27" s="26">
+        <f>AVERAGE(D22:D26)</f>
+        <v>91.8</v>
       </c>
-      <c r="E27" s="52">
-        <f t="shared" si="3"/>
-        <v>101.4</v>
+      <c r="E27" s="29">
+        <f>AVERAGE(E22:E26)</f>
+        <v>93.6</v>
       </c>
       <c r="F27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
@@ -3328,17 +3328,17 @@
     </row>
     <row r="28" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
-      <c r="B28" s="53" t="s">
-        <v>19</v>
+      <c r="B28" s="51" t="s">
+        <v>20</v>
       </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="55">
-        <f t="shared" ref="D28:E28" si="4">(2*6*10^-3-D27*633*10^-9)*(1-COS(RADIANS(10)))/(2*6*10^-3*(1-COS(RADIANS(10)))-D27*633*10^-9)</f>
-        <v>1.5079409552488516</v>
+      <c r="C28" s="52"/>
+      <c r="D28" s="30">
+        <f>(2*6*10^-3-D27*633*10^-9)*(1-COS(RADIANS(10)))/(2*6*10^-3*(1-COS(RADIANS(10)))-D27*633*10^-9)</f>
+        <v>1.4607706131046883</v>
       </c>
-      <c r="E28" s="56">
-        <f t="shared" si="4"/>
-        <v>1.5351393382012675</v>
+      <c r="E28" s="31">
+        <f>(2*6*10^-3-E27*633*10^-9)*(1-COS(RADIANS(10)))/(2*6*10^-3*(1-COS(RADIANS(10)))-E27*633*10^-9)</f>
+        <v>1.4741552755990384</v>
       </c>
       <c r="F28" s="3"/>
       <c r="I28" s="3"/>
@@ -3447,7 +3447,7 @@
     <row r="32" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -3476,26 +3476,26 @@
     </row>
     <row r="33" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
-      <c r="B33" s="6" t="s">
-        <v>21</v>
+      <c r="B33" s="44" t="s">
+        <v>22</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9">
+      <c r="C33" s="46"/>
+      <c r="D33" s="6">
         <v>3</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="6">
         <v>6</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="6">
         <v>9</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="6">
         <v>12</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="6">
         <v>15</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="7">
         <v>18</v>
       </c>
       <c r="J33" s="3"/>
@@ -3518,29 +3518,29 @@
     </row>
     <row r="34" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
-      <c r="B34" s="67" t="s">
-        <v>25</v>
+      <c r="B34" s="53" t="s">
+        <v>23</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="57">
-        <v>12</v>
+      <c r="D34" s="32">
+        <v>14</v>
       </c>
-      <c r="E34" s="58">
-        <v>21.5</v>
+      <c r="E34" s="33">
+        <v>20</v>
       </c>
-      <c r="F34" s="58">
-        <v>30.5</v>
+      <c r="F34" s="33">
+        <v>33</v>
       </c>
-      <c r="G34" s="58">
-        <v>41</v>
+      <c r="G34" s="33">
+        <v>38</v>
       </c>
-      <c r="H34" s="58">
-        <v>55.5</v>
+      <c r="H34" s="33">
+        <v>58</v>
       </c>
-      <c r="I34" s="59">
-        <v>68.5</v>
+      <c r="I34" s="34">
+        <v>65.5</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -3562,27 +3562,27 @@
     </row>
     <row r="35" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="13" t="s">
+      <c r="B35" s="54"/>
+      <c r="C35" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="58">
-        <v>10.5</v>
+      <c r="D35" s="33">
+        <v>9.5</v>
       </c>
-      <c r="E35" s="58">
-        <v>24</v>
+      <c r="E35" s="33">
+        <v>25</v>
       </c>
-      <c r="F35" s="58">
-        <v>31</v>
+      <c r="F35" s="33">
+        <v>28.5</v>
       </c>
-      <c r="G35" s="58">
-        <v>43.5</v>
+      <c r="G35" s="33">
+        <v>45</v>
       </c>
-      <c r="H35" s="58">
-        <v>53</v>
+      <c r="H35" s="33">
+        <v>51</v>
       </c>
-      <c r="I35" s="59">
-        <v>65</v>
+      <c r="I35" s="34">
+        <v>71</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -3604,27 +3604,27 @@
     </row>
     <row r="36" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="54"/>
+      <c r="C36" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="58">
-        <v>13</v>
+      <c r="D36" s="33">
+        <v>15</v>
       </c>
-      <c r="E36" s="58">
-        <v>20</v>
+      <c r="E36" s="33">
+        <v>18</v>
       </c>
-      <c r="F36" s="58">
-        <v>32.5</v>
+      <c r="F36" s="33">
+        <v>34.5</v>
       </c>
-      <c r="G36" s="58">
-        <v>39.5</v>
+      <c r="G36" s="33">
+        <v>37</v>
       </c>
-      <c r="H36" s="58">
-        <v>57</v>
+      <c r="H36" s="33">
+        <v>60</v>
       </c>
-      <c r="I36" s="59">
-        <v>69.5</v>
+      <c r="I36" s="34">
+        <v>66.5</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -3646,27 +3646,27 @@
     </row>
     <row r="37" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="54"/>
+      <c r="C37" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="58">
-        <v>11</v>
+      <c r="D37" s="33">
+        <v>10</v>
       </c>
-      <c r="E37" s="58">
-        <v>22.5</v>
+      <c r="E37" s="33">
+        <v>24.5</v>
       </c>
-      <c r="F37" s="58">
-        <v>29.5</v>
+      <c r="F37" s="33">
+        <v>27</v>
       </c>
-      <c r="G37" s="58">
-        <v>42</v>
+      <c r="G37" s="33">
+        <v>44</v>
       </c>
-      <c r="H37" s="58">
-        <v>54.5</v>
+      <c r="H37" s="33">
+        <v>52.5</v>
       </c>
-      <c r="I37" s="59">
-        <v>66</v>
+      <c r="I37" s="34">
+        <v>70</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -3688,27 +3688,27 @@
     </row>
     <row r="38" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="54"/>
+      <c r="C38" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="58">
-        <v>11.5</v>
+      <c r="D38" s="33">
+        <v>12.5</v>
       </c>
-      <c r="E38" s="58">
-        <v>21</v>
+      <c r="E38" s="33">
+        <v>20.5</v>
       </c>
-      <c r="F38" s="58">
-        <v>32</v>
+      <c r="F38" s="33">
+        <v>31</v>
       </c>
-      <c r="G38" s="58">
-        <v>40.5</v>
+      <c r="G38" s="33">
+        <v>41.5</v>
       </c>
-      <c r="H38" s="58">
-        <v>56</v>
+      <c r="H38" s="33">
+        <v>54</v>
       </c>
-      <c r="I38" s="59">
-        <v>67.5</v>
+      <c r="I38" s="34">
+        <v>68.5</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -3730,33 +3730,33 @@
     </row>
     <row r="39" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
-      <c r="B39" s="60"/>
-      <c r="C39" s="13" t="s">
-        <v>22</v>
+      <c r="B39" s="55"/>
+      <c r="C39" s="8" t="s">
+        <v>24</v>
       </c>
-      <c r="D39" s="61">
-        <f t="shared" ref="D39:I39" si="5">AVERAGE(D34:D38)</f>
-        <v>11.6</v>
+      <c r="D39" s="35">
+        <f t="shared" ref="D39:I39" si="1">AVERAGE(D34:D38)</f>
+        <v>12.2</v>
       </c>
-      <c r="E39" s="61">
-        <f t="shared" si="5"/>
-        <v>21.8</v>
+      <c r="E39" s="35">
+        <f t="shared" si="1"/>
+        <v>21.6</v>
       </c>
-      <c r="F39" s="61">
-        <f t="shared" si="5"/>
-        <v>31.1</v>
+      <c r="F39" s="35">
+        <f t="shared" si="1"/>
+        <v>30.8</v>
       </c>
-      <c r="G39" s="61">
-        <f t="shared" si="5"/>
-        <v>41.3</v>
+      <c r="G39" s="35">
+        <f t="shared" si="1"/>
+        <v>41.1</v>
       </c>
-      <c r="H39" s="61">
-        <f t="shared" si="5"/>
-        <v>55.2</v>
+      <c r="H39" s="35">
+        <f t="shared" si="1"/>
+        <v>55.1</v>
       </c>
-      <c r="I39" s="62">
-        <f t="shared" si="5"/>
-        <v>67.3</v>
+      <c r="I39" s="36">
+        <f t="shared" si="1"/>
+        <v>68.3</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -3778,32 +3778,32 @@
     </row>
     <row r="40" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
-      <c r="B40" s="66" t="s">
-        <v>24</v>
+      <c r="B40" s="40" t="s">
+        <v>25</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="63">
-        <f t="shared" ref="D40:I40" si="6">D33*633*10^-9/2/0.03*10^5</f>
+      <c r="C40" s="41"/>
+      <c r="D40" s="37">
+        <f t="shared" ref="D40:I40" si="2">D33*633*10^-9/2/0.03*10^5</f>
         <v>3.1650000000000005</v>
       </c>
-      <c r="E40" s="63">
-        <f t="shared" si="6"/>
+      <c r="E40" s="37">
+        <f t="shared" si="2"/>
         <v>6.330000000000001</v>
       </c>
-      <c r="F40" s="63">
-        <f t="shared" si="6"/>
+      <c r="F40" s="37">
+        <f t="shared" si="2"/>
         <v>9.495000000000001</v>
       </c>
-      <c r="G40" s="63">
-        <f t="shared" si="6"/>
+      <c r="G40" s="37">
+        <f t="shared" si="2"/>
         <v>12.660000000000002</v>
       </c>
-      <c r="H40" s="63">
-        <f t="shared" si="6"/>
+      <c r="H40" s="37">
+        <f t="shared" si="2"/>
         <v>15.825000000000003</v>
       </c>
-      <c r="I40" s="64">
-        <f t="shared" si="6"/>
+      <c r="I40" s="38">
+        <f t="shared" si="2"/>
         <v>18.990000000000002</v>
       </c>
       <c r="J40" s="3"/>
@@ -3856,12 +3856,12 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
@@ -3884,12 +3884,12 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="39"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -3912,12 +3912,12 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="39"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
@@ -3940,12 +3940,12 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="65"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="65"/>
-      <c r="H45" s="65"/>
-      <c r="I45" s="65"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
@@ -3968,12 +3968,12 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
@@ -3996,7 +3996,7 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="65"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -30706,25 +30706,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="B22:B26"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B4:B13"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
